--- a/database.xlsx
+++ b/database.xlsx
@@ -103,7 +103,7 @@
     <t>De Casteljau / Bézier</t>
   </si>
   <si>
-    <t>Diffusion Models on Toy Distributions</t>
+    <t>Diffusion Models on Three Dirac Atoms</t>
   </si>
   <si>
     <t>Dijkstra</t>
@@ -118,7 +118,7 @@
     <t>Edge Detection</t>
   </si>
   <si>
-    <t>Eikonal Distance with Dijkstra/Fast-Marching Intuition</t>
+    <t>Eikonal Distance and Fast-Marching Intuition</t>
   </si>
   <si>
     <t>Error Diffusion</t>
@@ -130,7 +130,7 @@
     <t>Farthest-Point Sampling</t>
   </si>
   <si>
-    <t>Finite Elements in 1D (Didactic Core)</t>
+    <t>Finite Element Method in 1D/2D</t>
   </si>
   <si>
     <t>Finite Group Representations and FFT on Cyclic Groups</t>
@@ -403,7 +403,7 @@
     <t>Matrix Completion via Nuclear Norm</t>
   </si>
   <si>
-    <t>Mean Curvature Flow of Planar Curves</t>
+    <t>Mean Curvature Flow of a Planar Curve</t>
   </si>
   <si>
     <t>Newton Fractals in the Complex Plane</t>
@@ -412,7 +412,7 @@
     <t>Normalizing Flows in 2D</t>
   </si>
   <si>
-    <t>Orthogonal Matching Pursuit</t>
+    <t>Orthogonal Matching Pursuit with Gaussian Bump Dictionary</t>
   </si>
   <si>
     <t>PageRank and Random Walks on Graphs</t>
@@ -448,7 +448,7 @@
     <t>Sinkhorn Distance and Entropic Optimal Transport</t>
   </si>
   <si>
-    <t>Sliced Wasserstein Geometry</t>
+    <t>Sliced Wasserstein Gradient Descent to a Target</t>
   </si>
   <si>
     <t>Spectral Graph Wavelets</t>
@@ -2491,13 +2491,13 @@
     <t>Builds a strong nonlinear classifier by iteratively combining weak separators.</t>
   </si>
   <si>
-    <t>For \min_x \tfrac12\|Ax-y\|_2^2 + \lambda\|x\|_1, split x=z and apply ADMM updates: x^{k+1}=\arg\min_x \tfrac12\|Ax-y\|_2^2+\frac{\rho}{2}\|x-z^k+u^k\|_2^2, z^{k+1}=\operatorname{soft}(x^{k+1}+u^k, \lambda/\rho), \quad u^{k+1}=u^k+x^{k+1}-z^{k+1}.</t>
+    <t>For split and apply ADMM updates:.</t>
   </si>
   <si>
     <t>Simulates transport of a scalar field by a smooth velocity flow on a periodic grid.</t>
   </si>
   <si>
-    <t>Two classic phase-field PDEs use the same double-well potential but different conservation laws: \partial_t u = \varepsilon^2 \Delta u - (u^3-u) \quad \text{(Allen–Cahn)}, \partial_t u = \Delta\! \left(-\varepsilon^2 \Delta u + (u^3-u)\right) \quad \text{(C...</t>
+    <t>Two classic phase-field PDEs use the same double-well potential but different conservation laws: Allen–Cahn is non-conservative; Cahn–Hilliard conserves mass.</t>
   </si>
   <si>
     <t>Reconstructs multiscale geometry and boundaries from scattered planar point clouds.</t>
@@ -2524,7 +2524,7 @@
     <t>Illustrates central-limit behavior through repeated convolution of discrete laws.</t>
   </si>
   <si>
-    <t>BFGS builds curvature information through rank-two Hessian-inverse updates: H_{k+1}=(I-\rho s y^\top)H_k(I-\rho y s^\top)+\rho ss^\top, \quad \rho=\frac1{y^\top s}. This often accelerates convergence on ill-conditioned smooth objectives.</t>
+    <t>BFGS builds curvature information through rank-two Hessian-inverse updates: This often accelerates convergence on ill-conditioned smooth objectives.</t>
   </si>
   <si>
     <t>Explores period-doubling and chaos in iterated logistic dynamics.</t>
@@ -2551,10 +2551,10 @@
     <t>Explores Wolfram's 256 elementary rules and Conway's Game of Life on 1D and 2D grids.</t>
   </si>
   <si>
-    <t>Uniform approximation seeks p_n minimizing \|f-p_n\|_{\infty, [-1, 1]}. Chebyshev interpolation is near-minimax in many practical settings and avoids Runge oscillations. We compare Taylor and Chebyshev polynomial approximations.</t>
-  </si>
-  <si>
-    <t>Recover sparse x^\star from underdetermined measurements y=Ax^\star by solving \min_x \|x\|_1 \quad \text{s.t.}\quad Ax=y or its penalized version (LASSO): \min_x \tfrac12\|Ax-y\|_2^2+\lambda\|x\|_1.</t>
+    <t>Uniform approximation seeks minimizing Chebyshev interpolation is near-minimax in many practical settings and avoids Runge oscillations. We compare Taylor and Chebyshev polynomial approximations.</t>
+  </si>
+  <si>
+    <t>Recover sparse from underdetermined measurements by solving or its penalized version (LASSO):.</t>
   </si>
   <si>
     <t>Visualizes Krylov subspace search paths and the effect of condition number on convergence speed.</t>
@@ -2563,7 +2563,7 @@
     <t>Constructs Bézier curves via the De Casteljau triangular scheme and demonstrates subdivision.</t>
   </si>
   <si>
-    <t>In discrete-time diffusion, x_t = \sqrt{\bar\alpha_t}\, x_0 + \sqrt{1-\bar\alpha_t}\, \epsilon, \qquad \epsilon\sim\mathcal N(0, I). We illustrate forward noising and a simple denoising proxy on a 2D ring distribution.</t>
+    <t>We start from a distribution with Dirac atoms: Under Gaussian forward noising, each atom becomes a Gaussian component, so which gives a closed-form score.</t>
   </si>
   <si>
     <t>Computes shortest paths on weighted grid graphs and visualizes wavefront expansion through heterogeneous terrain.</t>
@@ -2578,7 +2578,7 @@
     <t>Implements gradient, Laplacian zero-crossing, and Canny detectors across a Gaussian scale-space.</t>
   </si>
   <si>
-    <t>The eikonal equation \|\nabla T(x)\| = \frac{1}{f(x)} describes travel time in a medium with speed f(x). On grids, Dijkstra/Fast-Marching style updates propagate a monotone front.</t>
+    <t>For speed, the arrival time solves We design as a smooth mixture of two bumps so geodesics avoid the center, and visualize front propagation snapshots.</t>
   </si>
   <si>
     <t>Halftones continuous-tone images using Floyd–Steinberg error diffusion and contrasts Bayer and random dithering.</t>
@@ -2590,10 +2590,10 @@
     <t>Builds well-spread point sets via a greedy covering algorithm and visualizes the evolving Voronoi diagram.</t>
   </si>
   <si>
-    <t>We solve -u''(x)=f(x) on (0, 1) with Dirichlet boundary conditions using piecewise-linear finite elements. The weak form reads \int_0^1 u'(x)v'(x)\, dx = \int_0^1 f(x)v(x)\, dx \quad \forall v\in H_0^1.</t>
-  </si>
-  <si>
-    <t>On the cyclic group \mathbb Z_n, irreducible characters are \chi_k(t)=e^{-2\pi i kt/n}. The DFT diagonalizes circular convolution, which is the group algebra product.</t>
+    <t>We solve on with homogeneous Dirichlet boundaries and compare six mesh resolutions to show convergence.</t>
+  </si>
+  <si>
+    <t>On the cyclic group, irreducible characters are The DFT diagonalizes circular convolution, which is the group algebra product.</t>
   </si>
   <si>
     <t>Visualizes cobweb diagrams, Banach's theorem, and convergence rates for one-dimensional contractions.</t>
@@ -2611,7 +2611,7 @@
     <t>Explores 1D and 2D Fourier atoms, the DFT matrix, and Gram-matrix orthogonality of sinusoidal bases.</t>
   </si>
   <si>
-    <t>Generates crystallographic and quasicrystalline interference patterns from K -fold symmetric plane waves.</t>
+    <t>Generates crystallographic and quasicrystalline interference patterns from -fold symmetric plane waves.</t>
   </si>
   <si>
     <t>Approximates closed planar curves with bandlimited Fourier descriptors and sweeps the bandwidth interactively.</t>
@@ -2626,13 +2626,13 @@
     <t>Simulates spatially-varyingg Gaussian blur mimicking the foveal acuity falloff of the human retina.</t>
   </si>
   <si>
-    <t>Applies the Fourier definition of fractional derivatives to a Gaussian and sweeps the order \alpha \in [0, 4].</t>
+    <t>Applies the Fourier definition of fractional derivatives to a Gaussian and sweeps the order.</t>
   </si>
   <si>
     <t>Computes convergents via the Euclidean algorithm, verifies best-approximation and the Gauss–Kuzmin distribution.</t>
   </si>
   <si>
-    <t>Explores the nonlocal operator (-\Delta)^s via its Fourier multiplier, anomalous diffusion, and Lévy-flight tails.</t>
+    <t>Explores the nonlocal operator via its Fourier multiplier, anomalous diffusion, and Lévy-flight tails.</t>
   </si>
   <si>
     <t>Implements the projection-free Frank–Wolfe algorithm on polytopes and visualizes the sparse iterate trajectory.</t>
@@ -2647,7 +2647,7 @@
     <t>Plots closed-form level sets of KL, Hellinger, Wasserstein-2, and Fisher–Rao divergences on the Gaussian manifold.</t>
   </si>
   <si>
-    <t>A Gaussian process prior is f \sim \mathcal{GP}(0, k_\theta(\cdot, \cdot)). Posterior mean and variance are computed with kernel matrices. We illustrate 2D regression with uncertainty maps.</t>
+    <t>A Gaussian process prior is Posterior mean and variance are computed with kernel matrices. We illustrate 2D regression with uncertainty maps.</t>
   </si>
   <si>
     <t>Visualizes how product (precision sum) and convolution (covariance sum) reshape Gaussian confidence ellipses.</t>
@@ -2668,7 +2668,7 @@
     <t>MCMC on a multiwell 2D energy: explores the effect of temperature ε on chain mixing, acceptance rate, and autocorrelation.</t>
   </si>
   <si>
-    <t>A basic message passing layer reads H^{(\ell+1)} = \sigma(\tilde D^{-1/2}\tilde A\tilde D^{-1/2} H^{(\ell)} W^{(\ell)}). We run a small two-layer GCN-style propagation and inspect feature separation.</t>
+    <t>A basic message passing layer reads We run a small two-layer GCN-style propagation and inspect feature separation.</t>
   </si>
   <si>
     <t>Visualises gradient descent trajectories on the banana function for multiple step sizes and starting points, with interactive step-size control.</t>
@@ -2707,7 +2707,7 @@
     <t>Implements fast Haar transform and Hadamard–Walsh transform; visualises multiresolution decomposition and hard-thresholding denoising.</t>
   </si>
   <si>
-    <t>For a Hamiltonian H(q, p)=\frac12 p^2 + V(q), equations of motion are \dot q = \partial_p H, \qquad \dot p = -\partial_q H. Symplectic schemes (like Störmer–Verlet) preserve geometric structure and usually control long-time energy drift better than explicit...</t>
+    <t>Hamiltonian particle systems are a core model for mechanics, molecular dynamics, and statistical physics. For a state with position and momentum, the dynamics is The key numerical question is not only short-term accuracy, but also long-term geometric fideli...</t>
   </si>
   <si>
     <t>Solves the 2D Laplace equation with various Dirichlet boundary conditions and illustrates the orthogonal families of harmonic conjugate level sets.</t>
@@ -2737,7 +2737,7 @@
     <t>Equalizes image histograms via the empirical CDF rank transform and performs histogram matching as 1D optimal transport.</t>
   </si>
   <si>
-    <t>An HMM has latent states x_t and observations y_t with p(x_{1:T}, y_{1:T}) = p(x_1)\prod_{t=2}^{T}p(x_t|x_{t-1})\prod_{t=1}^{T}p(y_t|x_t). We compute filtering probabilities and the most likely latent path.</t>
+    <t>An HMM has latent states and observations with We compute filtering probabilities and the most likely latent path.</t>
   </si>
   <si>
     <t>Visualizes the Hölder defect on 2D grids and plots conjugate Lp/Lq unit balls as polar dual convex bodies.</t>
@@ -2854,70 +2854,70 @@
     <t>Computes convex conjugates via the Legendre-Fenchel transform; illustrates subdifferentials, the bidual theorem, and inf-convolution as a Minkowski sum.</t>
   </si>
   <si>
-    <t>A moving interface \Gamma_t can be represented as \{\phi(\cdot, t)=0\}. Under advection velocity v, the level-set PDE is \partial_t \phi + v\cdot\nabla\phi = 0. We illustrate transport of an implicit curve and periodic reinitialization to signed-distance sh...</t>
-  </si>
-  <si>
-    <t>For a stochastic matrix P, the distribution evolves as \pi_{t+1} = \pi_t P. Mixing speed is linked to the spectral gap 1-|\lambda_2|. We compare total variation decay from different starts.</t>
-  </si>
-  <si>
-    <t>Matrix completion solves \min_X \frac12\|P_\Omega(X-M)\|_F^2 + \lambda \|X\|_. The proximal step of \|\cdot\|_ is singular-value soft-thresholding. We recover a low-rank matrix from random missing entries.</t>
-  </si>
-  <si>
-    <t>For a curve \Gamma_t, mean-curvature flow evolves normal velocity as: V_n = -\kappa, which smooths and shrinks shapes. In discrete form, Laplacian smoothing of polygon vertices provides a didactic approximation.</t>
-  </si>
-  <si>
-    <t>For a polynomial p(z), Newton's method iterates z_{k+1} = z_k - \frac{p(z_k)}{p'(z_k)}. Each initial point converges to a root (when it converges), and the basin partition creates a fractal boundary. This notebook visualizes both the attraction basins and c...</t>
-  </si>
-  <si>
-    <t>A normalizing flow composes invertible maps z_{k+1} = T_k(z_k), \qquad \log p_X(x)=\log p_Z(z)-\sum_k \log|\det J_{T_k}(z_k)|. We build a didactic affine-coupling flow and visualize transformed samples.</t>
-  </si>
-  <si>
-    <t>OMP greedily builds sparse approximations by repeatedly selecting the atom most correlated with the residual and refitting coefficients by least squares. At step k: j_k=\arg\max_j |\langle a_j, r_{k-1}\rangle|, \qquad x_{S_k}=\arg\min_z\|A_{S_k}z-y\|_2^2.</t>
-  </si>
-  <si>
-    <t>PageRank is the stationary distribution of \pi = \alpha P^\top \pi + (1-\alpha) v, where teleportation vector v guarantees ergodicity. We study ranking changes with \alpha.</t>
-  </si>
-  <si>
-    <t>Particle filters approximate p(x_t|y_{1:t}) by weighted particles \sum_{i=1}^N w_t^{(i)} \delta(x_t-x_t^{(i)}). We illustrate importance weighting, effective sample size, and systematic resampling.</t>
-  </si>
-  <si>
-    <t>For problems \min_x f(Kx)+g(x), PDHG updates y^{k+1}=\operatorname{prox}_{\sigma f^\ }(y^k+\sigma K\bar x^k), \quad x^{k+1}=\operatorname{prox}_{\tau g}(x^k-\tau K^\top y^{k+1}), with extrapolation \bar x^{k+1}=x^{k+1}+\theta(x^{k+1}-x^k). We demonstrate de...</t>
-  </si>
-  <si>
-    <t>Persistent homology tracks birth/death of topological features across scales. For connected components ( H_0 ), bar lengths are related to MST edge lengths. We illustrate H_0 persistence on point clouds with two clusters.</t>
-  </si>
-  <si>
-    <t>On a graph/mesh discretization, a Poisson problem can be written as L u = f, with fixed boundary values. This notebook demonstrates harmonic/Poisson solves on a 2D triangulated square.</t>
-  </si>
-  <si>
-    <t>Reaction-diffusion systems couple local nonlinear chemistry and diffusion: \partial_t U = D_u \Delta U - UV^2 + F(1-U), \qquad \partial_t V = D_v \Delta V + UV^2 - (F+k)V. Different (F, k) regimes yield spots, stripes, and labyrinths.</t>
-  </si>
-  <si>
-    <t>On the Stiefel manifold St(p, n)=\{X\in\mathbb R^{n\times p}:X^\top X=I\}, we optimize with tangent projection and retraction: X_{k+1} = \mathrm{qf}(X_k - \eta \, \mathrm{grad} f(X_k)). We solve a PCA-style objective under orthogonality constraints.</t>
-  </si>
-  <si>
-    <t>Principal component pursuit solves \min_{L, S}\ \|L\|_ + \lambda\|S\|_1 \quad \text{s.t.} \quad M=L+S. We use an inexact augmented Lagrangian style iteration to separate structured and sparse components.</t>
-  </si>
-  <si>
-    <t>For the test equation \dot y=\lambda y, a one-step method induces y_{n+1}=R(z) y_n, \qquad z=h\lambda. Absolute stability requires |R(z)|\leq 1. We compare Euler, RK2, and RK4 stability regions.</t>
-  </si>
-  <si>
-    <t>The Schrödinger bridge builds the most likely stochastic evolution between fixed marginals under a diffusion prior. In discrete settings, it is tightly connected to entropic OT couplings: \gamma^\star = \arg\min_{\gamma \in \Pi(a, b)} \langle C, \gamma\rang...</t>
-  </si>
-  <si>
-    <t>Optimal transport compares probability measures by minimizing the cost of moving mass: \min_{\gamma \in \Pi(a, b)} \langle C, \gamma \rangle, where \Pi(a, b) is the set of couplings with prescribed marginals a and b.</t>
-  </si>
-  <si>
-    <t>Sliced Wasserstein distances project high-dimensional measures onto 1D lines, where OT is cheap: \mathrm{SW}_2^2(\mu, \nu)=\int_{\theta \in \mathbb{S}^{d-1}} W_2^2(P_\theta\#\mu, \ P_\theta\#\nu)\, d\theta. Monte Carlo over random directions gives scalable...</t>
-  </si>
-  <si>
-    <t>For graph Laplacian L=U\Lambda U^\top, spectral filtering applies g(L) = U g(\Lambda) U^\top. Wavelets localize by choosing band-pass kernels at multiple scales. We show scale effects on a ring graph signal.</t>
-  </si>
-  <si>
-    <t>Spherical harmonics form an orthonormal basis on \mathbb S^2: f(\theta, \phi)=\sum_{\ell=0}^{\infty}\sum_{m=-\ell}^{\ell} c_{\ell m}Y_\ell^m(\theta, \phi). We use low-order real harmonics to synthesize and visualize a band-limited signal.</t>
-  </si>
-  <si>
-    <t>Trust-region methods solve local quadratic models \min_{\|p\|\le \Delta_k}\ m_k(p)=f(x_k)+g_k^\top p+\tfrac12 p^\top B_k p, and adapt radius \Delta_k using agreement ratio between actual and predicted decrease.</t>
+    <t>A moving interface can be represented as. Under advection velocity, the level-set PDE is We illustrate transport of an implicit curve and periodic reinitialization to signed-distance shape.</t>
+  </si>
+  <si>
+    <t>For a stochastic matrix, the distribution evolves as Mixing speed is linked to the spectral gap. We compare total variation decay from different starts.</t>
+  </si>
+  <si>
+    <t>Matrix completion solves The proximal step of is singular-value soft-thresholding. We recover a low-rank matrix from random missing entries.</t>
+  </si>
+  <si>
+    <t>For a planar curve parametrized by arc length, mean-curvature flow obeys where is scalar curvature and is the inward normal. Using a periodic polygonal discretization, we approximate and evolve for a longer horizon from a less regular initial curve.</t>
+  </si>
+  <si>
+    <t>For a polynomial, Newton's method iterates Each initial point converges to a root (when it converges), and the basin partition creates a fractal boundary. This notebook visualizes both the attraction basins and convergence speed.</t>
+  </si>
+  <si>
+    <t>A normalizing flow composes invertible maps We build a didactic affine-coupling flow and visualize transformed samples.</t>
+  </si>
+  <si>
+    <t>Given a dictionary and a signal, OMP iteratively selects atoms maximizing correlation with residuals: We use a Gaussian bump dictionary and reconstruct a sparse smooth signal.</t>
+  </si>
+  <si>
+    <t>PageRank is the stationary distribution of where teleportation vector guarantees ergodicity. We study ranking changes with.</t>
+  </si>
+  <si>
+    <t>Particle filters approximate by weighted particles We illustrate importance weighting, effective sample size, and systematic resampling.</t>
+  </si>
+  <si>
+    <t>For problems, PDHG updates with extrapolation. We demonstrate denoising with TV-like finite differences.</t>
+  </si>
+  <si>
+    <t>Persistent homology tracks birth/death of topological features across scales. For connected components ( ), bar lengths are related to MST edge lengths. We illustrate persistence on point clouds with two clusters.</t>
+  </si>
+  <si>
+    <t>On a graph/mesh discretization, a Poisson problem can be written as with fixed boundary values. This notebook demonstrates harmonic/Poisson solves on a 2D triangulated square.</t>
+  </si>
+  <si>
+    <t>Reaction-diffusion systems couple local nonlinear chemistry and diffusion: Different regimes yield spots, stripes, and labyrinths.</t>
+  </si>
+  <si>
+    <t>On the Stiefel manifold, we optimize with tangent projection and retraction: We solve a PCA-style objective under orthogonality constraints.</t>
+  </si>
+  <si>
+    <t>Principal component pursuit solves We use an inexact augmented Lagrangian style iteration to separate structured and sparse components.</t>
+  </si>
+  <si>
+    <t>For the test equation, a one-step method induces Absolute stability requires. We compare Euler, RK2, and RK4 stability regions.</t>
+  </si>
+  <si>
+    <t>The Schrödinger bridge builds the most likely stochastic evolution between fixed marginals under a diffusion prior. In discrete settings, it is tightly connected to entropic OT couplings: This notebook visualizes entropic interpolation between 1D marginals.</t>
+  </si>
+  <si>
+    <t>Optimal transport compares probability measures by minimizing the cost of moving mass: where is the set of couplings with prescribed marginals and.</t>
+  </si>
+  <si>
+    <t>The sliced Wasserstein distance between empirical measures is We optimize source particles by gradient descent to match a target distribution, and ensure good final alignment.</t>
+  </si>
+  <si>
+    <t>For graph Laplacian, spectral filtering applies Wavelets localize by choosing band-pass kernels at multiple scales. We show scale effects on a ring graph signal.</t>
+  </si>
+  <si>
+    <t>Spherical harmonics form an orthonormal basis on: We use low-order real harmonics to synthesize and visualize a band-limited signal.</t>
+  </si>
+  <si>
+    <t>Trust-region methods solve local quadratic models and adapt radius using agreement ratio between actual and predicted decrease.</t>
   </si>
   <si>
     <t>Dimensionality reduction balances neighborhood preservation and global geometry. We compare PCA, a t-SNE-like neighborhood embedding objective, and a graph-spectral embedding in a didactic pipeline.</t>
@@ -2926,13 +2926,13 @@
     <t>Classical transport enforces exact mass conservation. Unbalanced OT relaxes this by penalizing marginal mismatch, which is essential when sources and targets have different total mass.</t>
   </si>
   <si>
-    <t>Mean-field VI maximizes an ELBO \mathcal{L}(q)=\mathbb{E}_q[\log p(X, Z, \Theta)]-\mathbb{E}_q[\log q(Z, \Theta)]. For didactic clarity we run soft-EM style coordinate updates and monitor the objective.</t>
-  </si>
-  <si>
-    <t>Given distributions (\mu_i) and weights (\lambda_i), a Wasserstein barycenter minimizes \nu^\star = \arg\min_\nu \sum_i \lambda_i W_2^2(\nu, \mu_i). In one dimension, this has a simple quantile formula: Q_{\nu^\star}(t) = \sum_i \lambda_i Q_{\mu_i}(t). This...</t>
-  </si>
-  <si>
-    <t>For u_{tt}=c^2u_{xx}, the exact phase speed is frequency-independent ( \omega=ck ). Discrete schemes introduce modified dispersion: \sin^2\! \left(\frac{\omega\Delta t}{2}\right) = r^2\sin^2\! \left(\frac{k\Delta x}{2}\right), \quad r=\frac{c\Delta t}{\Delt...</t>
+    <t>Mean-field VI maximizes an ELBO For didactic clarity we run soft-EM style coordinate updates and monitor the objective.</t>
+  </si>
+  <si>
+    <t>Given distributions and weights, a Wasserstein barycenter minimizes In one dimension, this has a simple quantile formula: This notebook illustrates barycenter shape interpolation in 1D.</t>
+  </si>
+  <si>
+    <t>For, the exact phase speed is frequency-independent ( ). Discrete schemes introduce modified dispersion: This notebook compares analytical and numerical behavior.</t>
   </si>
   <si>
     <t>The Kubo-Ando mean generalizes geometric mean to matrices and preserves key properties (e.g. concavity and arithmetic-geometric inequality). https://link.springer.com/content/pdf/10.1007/BF01371042.pdf</t>

--- a/database.xlsx
+++ b/database.xlsx
@@ -118,7 +118,7 @@
     <t>Edge Detection</t>
   </si>
   <si>
-    <t>Eikonal Distance and Fast-Marching Intuition</t>
+    <t>Eikonal Equation and Fast Marching Method</t>
   </si>
   <si>
     <t>Error Diffusion</t>
@@ -130,7 +130,7 @@
     <t>Farthest-Point Sampling</t>
   </si>
   <si>
-    <t>Finite Element Method in 1D/2D</t>
+    <t>Finite Element Method in 1D</t>
   </si>
   <si>
     <t>Finite Group Representations and FFT on Cyclic Groups</t>
@@ -412,7 +412,7 @@
     <t>Normalizing Flows in 2D</t>
   </si>
   <si>
-    <t>Orthogonal Matching Pursuit with Gaussian Bump Dictionary</t>
+    <t>Orthogonal Matching Pursuit with a Gaussian Bump Dictionary</t>
   </si>
   <si>
     <t>PageRank and Random Walks on Graphs</t>
@@ -448,7 +448,7 @@
     <t>Sinkhorn Distance and Entropic Optimal Transport</t>
   </si>
   <si>
-    <t>Sliced Wasserstein Gradient Descent to a Target</t>
+    <t>Sliced Wasserstein Gradient Descent</t>
   </si>
   <si>
     <t>Spectral Graph Wavelets</t>
@@ -2563,7 +2563,7 @@
     <t>Constructs Bézier curves via the De Casteljau triangular scheme and demonstrates subdivision.</t>
   </si>
   <si>
-    <t>We start from a distribution with Dirac atoms: Under Gaussian forward noising, each atom becomes a Gaussian component, so which gives a closed-form score.</t>
+    <t>Denoising Diffusion Probabilistic Models (DDPM) learn to reverse a Markov noising process. By choosing a distribution simple enough to admit a closed-form score, we can study both the forward and reverse dynamics exactly — without training a neural network.</t>
   </si>
   <si>
     <t>Computes shortest paths on weighted grid graphs and visualizes wavefront expansion through heterogeneous terrain.</t>
@@ -2578,7 +2578,7 @@
     <t>Implements gradient, Laplacian zero-crossing, and Canny detectors across a Gaussian scale-space.</t>
   </si>
   <si>
-    <t>For speed, the arrival time solves We design as a smooth mixture of two bumps so geodesics avoid the center, and visualize front propagation snapshots.</t>
+    <t>Given a spatially varyingg speed function, the eikonal equation models the arrival time of a wavefront emanating from a source: Equivalently, is the geodesic (weighted shortest path) distance from to.</t>
   </si>
   <si>
     <t>Halftones continuous-tone images using Floyd–Steinberg error diffusion and contrasts Bayer and random dithering.</t>
@@ -2590,7 +2590,7 @@
     <t>Builds well-spread point sets via a greedy covering algorithm and visualizes the evolving Voronoi diagram.</t>
   </si>
   <si>
-    <t>We solve on with homogeneous Dirichlet boundaries and compare six mesh resolutions to show convergence.</t>
+    <t>The Finite Element Method (FEM) is one of the most widely used numerical techniques for solving partial differential equations. It is the backbone of structural analysis, fluid dynamics, electromagnetics, and many other fields.</t>
   </si>
   <si>
     <t>On the cyclic group, irreducible characters are The DFT diagonalizes circular convolution, which is the group algebra product.</t>
@@ -2863,7 +2863,7 @@
     <t>Matrix completion solves The proximal step of is singular-value soft-thresholding. We recover a low-rank matrix from random missing entries.</t>
   </si>
   <si>
-    <t>For a planar curve parametrized by arc length, mean-curvature flow obeys where is scalar curvature and is the inward normal. Using a periodic polygonal discretization, we approximate and evolve for a longer horizon from a less regular initial curve.</t>
+    <t>Mean curvature flow is a geometric evolution equation that moves a curve (or surface) in the direction of its curvature vector. For a smooth planar curve parametrized over, the flow reads where is the signed curvature and is the inward unit normal.</t>
   </si>
   <si>
     <t>For a polynomial, Newton's method iterates Each initial point converges to a root (when it converges), and the basin partition creates a fractal boundary. This notebook visualizes both the attraction basins and convergence speed.</t>
@@ -2872,7 +2872,7 @@
     <t>A normalizing flow composes invertible maps We build a didactic affine-coupling flow and visualize transformed samples.</t>
   </si>
   <si>
-    <t>Given a dictionary and a signal, OMP iteratively selects atoms maximizing correlation with residuals: We use a Gaussian bump dictionary and reconstruct a sparse smooth signal.</t>
+    <t>Orthogonal Matching Pursuit (OMP) is a greedy algorithm for sparse signal approximation. Given a signal and an overcomplete dictionary (with ), OMP finds a sparse representation by iteratively selecting the atom most correlated with the current residual, th...</t>
   </si>
   <si>
     <t>PageRank is the stationary distribution of where teleportation vector guarantees ergodicity. We study ranking changes with.</t>
@@ -2908,7 +2908,7 @@
     <t>Optimal transport compares probability measures by minimizing the cost of moving mass: where is the set of couplings with prescribed marginals and.</t>
   </si>
   <si>
-    <t>The sliced Wasserstein distance between empirical measures is We optimize source particles by gradient descent to match a target distribution, and ensure good final alignment.</t>
+    <t>The Wasserstein distance between two probability measures quantifies the minimal transport cost to morph one distribution into the other. Computing in high dimension is expensive ( for discrete measures of size ). The sliced Wasserstein distance sidesteps t...</t>
   </si>
   <si>
     <t>For graph Laplacian, spectral filtering applies Wavelets localize by choosing band-pass kernels at multiple scales. We show scale effects on a ring graph signal.</t>
